--- a/artfynd/A 16079-2026 artfynd.xlsx
+++ b/artfynd/A 16079-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>133883044</v>
       </c>
       <c r="B3" t="n">
-        <v>111196</v>
+        <v>111203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 16079-2026 artfynd.xlsx
+++ b/artfynd/A 16079-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>122118598</v>
       </c>
       <c r="B2" t="n">
-        <v>110850</v>
+        <v>111128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133883044</v>
+        <v>133878143</v>
       </c>
       <c r="B3" t="n">
-        <v>111203</v>
+        <v>111210</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -826,16 +826,17 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Abullaberga, 600 m Norr, Småvänderot, Sk</t>
+          <t>Abullaberga, 700 m VNV, Småvänderot, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432659</v>
+        <v>432484</v>
       </c>
       <c r="R3" t="n">
-        <v>6186730</v>
+        <v>6186803</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +863,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>M-Kri-2626</t>
+          <t>M-Kri-2473</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -873,6 +874,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Båda sidor om vägen och båda sidor om bäcken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,6 +887,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,6 +903,123 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133883044</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111210</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Abullaberga, 600 m Norr, Småvänderot, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>432659</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6186730</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Huaröd</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>M-Kri-2626</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Mats Eneberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 16079-2026 artfynd.xlsx
+++ b/artfynd/A 16079-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122118598</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133878143</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,8 +1039,18 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883044</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>